--- a/tests/fixtures/xlsx/chart-image.xlsx
+++ b/tests/fixtures/xlsx/chart-image.xlsx
@@ -110,24 +110,78 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"><xdr:oneCellAnchor editAs="oneCell"><xdr:from><xdr:col>3</xdr:col><xdr:colOff>0</xdr:colOff><xdr:row>1</xdr:row><xdr:rowOff>0</xdr:rowOff></xdr:from><xdr:ext cx="609600" cy="609600"/><xdr:pic><xdr:nvPicPr><xdr:cNvPr id="1" name="Picture 1"><a:extLst><a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}"><a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/></a:ext></a:extLst></xdr:cNvPr><xdr:cNvPicPr><a:picLocks noChangeAspect="1"/></xdr:cNvPicPr></xdr:nvPicPr><xdr:blipFill><a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/><a:stretch><a:fillRect/></a:stretch></xdr:blipFill><xdr:spPr><a:xfrm><a:off x="0" y="0"/><a:ext cx="0" cy="0"/></a:xfrm><a:prstGeom prst="rect"><a:avLst/></a:prstGeom></xdr:spPr></xdr:pic><xdr:clientData/></xdr:oneCellAnchor><xdr:twoCellAnchor xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:from><xdr:col>5</xdr:col><xdr:colOff>0</xdr:colOff><xdr:row>1</xdr:row><xdr:rowOff>0</xdr:rowOff></xdr:from>
-  <xdr:to><xdr:col>10</xdr:col><xdr:colOff>0</xdr:colOff><xdr:row>10</xdr:row><xdr:rowOff>0</xdr:rowOff></xdr:rowOff></xdr:to>
-  <xdr:graphicFrame macro="">
-    <xdr:nvGraphicFramePr>
-      <xdr:cNvPr id="2" name="Chart 1"/>
-      <xdr:cNvGraphicFramePr/>
-    </xdr:nvGraphicFramePr>
-    <xdr:xfrm><a:off x="0" y="0"/><a:ext cx="0" cy="0"/></xdr:xfrm>
-    <a:graphic>
-      <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-        <c:chart r:id="rIdChart1"/>
-      </a:graphicData>
-    </a:graphic>
-  </xdr:graphicFrame>
-  <xdr:clientData/>
-</xdr:twoCellAnchor></xdr:wsDr>
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="609600" cy="609600"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rIdChart1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
